--- a/output/pdf_financials_xlsx/JEC.xlsx
+++ b/output/pdf_financials_xlsx/JEC.xlsx
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.002497</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.020579</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0</v>
@@ -50784,7 +50784,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E453" s="5" t="n">
         <v>-0.002497</v>
       </c>

--- a/output/pdf_financials_xlsx/JEC.xlsx
+++ b/output/pdf_financials_xlsx/JEC.xlsx
@@ -67908,7 +67908,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E633" s="5" t="n">

--- a/output/pdf_financials_xlsx/JEC.xlsx
+++ b/output/pdf_financials_xlsx/JEC.xlsx
@@ -2028,13 +2028,13 @@
         <v>0</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.003917</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="29">
@@ -2083,13 +2083,13 @@
         <v>-2.790934</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.638324</v>
+        <v>-4.634407</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.291344</v>
+        <v>-2.244344</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.942387</v>
+        <v>-1.895387</v>
       </c>
     </row>
     <row r="30">
@@ -2142,13 +2142,13 @@
         <v>-23.27109633969767</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-70.21563383121692</v>
+        <v>-70.15633770664328</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-59.37521054175438</v>
+        <v>-58.15730747025466</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-52.44768764471206</v>
+        <v>-51.17860927912299</v>
       </c>
     </row>
     <row r="31">
@@ -5996,13 +5996,13 @@
         <v>0</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.003917</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="101">
@@ -6644,7 +6644,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.016196</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -32656,7 +32656,11 @@
           <t>Depreciation of right-of-use assets (note 18)</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -36420,7 +36424,11 @@
           <t>Depreciation of right-of-use assets (note 21)</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -40470,7 +40478,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/JEC.xlsx
+++ b/output/pdf_financials_xlsx/JEC.xlsx
@@ -2465,31 +2465,31 @@
         <v>5.844376</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>1.17113</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>1.641737</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>4.61254</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0</v>
+        <v>5.534608</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0</v>
+        <v>7.654288</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0</v>
+        <v>7.090572</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0</v>
+        <v>0.571761</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0</v>
+        <v>9.084118</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>0</v>
+        <v>12.872535</v>
       </c>
     </row>
     <row r="38">
@@ -2630,31 +2630,31 @@
         <v>0.273201</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.340023</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.462271</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.206475</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.311803</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.533982</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.272992</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.257074</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>1.03707</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>0.907242</v>
       </c>
     </row>
     <row r="41">
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>0.272968</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>0.282187</v>
       </c>
       <c r="K56" s="3" t="n">
         <v>0</v>
@@ -3601,10 +3601,10 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>0.032448</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>0.088728</v>
       </c>
       <c r="K57" s="3" t="n">
         <v>0</v>
@@ -3998,31 +3998,31 @@
         <v>0.472273</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>1.553297</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.762115</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.12713</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.144931</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.07585500000000001</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.078457</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.189262</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.091132</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.019456</v>
       </c>
     </row>
     <row r="65">
@@ -4163,31 +4163,31 @@
         <v>0.398518</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.438745</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.82062</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.963495</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>1.28814</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>1.698336</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>1.33818</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>1.563874</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>10.748149</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>14.053828</v>
       </c>
     </row>
     <row r="68">
@@ -4346,13 +4346,13 @@
         <v>0</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.052937</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.04734</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.060253</v>
       </c>
     </row>
     <row r="71">
@@ -4401,13 +4401,13 @@
         <v>0</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.052937</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.04734</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.060253</v>
       </c>
     </row>
     <row r="72">
@@ -4624,10 +4624,10 @@
         <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>2.757133</v>
+        <v>2.709793</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>2.776649</v>
+        <v>2.716396</v>
       </c>
     </row>
     <row r="76">
@@ -4926,15 +4926,13 @@
         </is>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.003973035663774238</v>
+        <v>0.006375793354396252</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.00274655298016137</v>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004866865724051643</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.002369638983320145</v>
       </c>
     </row>
     <row r="81">
@@ -7047,10 +7045,8 @@
       <c r="O119" s="3" t="n">
         <v>-0.278635</v>
       </c>
-      <c r="P119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P119" s="3" t="n">
+        <v>0.519001</v>
       </c>
       <c r="Q119" s="1" t="inlineStr">
         <is>
@@ -7613,15 +7609,11 @@
       <c r="G129" s="3" t="n">
         <v>5.834716</v>
       </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H129" s="3" t="n">
+        <v>-0.575516</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>4.711191</v>
       </c>
       <c r="J129" s="3" t="n">
         <v>2.022555</v>
@@ -7953,15 +7945,11 @@
       <c r="G135" s="3" t="n">
         <v>-2.316011</v>
       </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H135" s="3" t="n">
+        <v>3.476982</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>2.090492</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>7.314076</v>
@@ -7981,15 +7969,11 @@
       <c r="O135" s="3" t="n">
         <v>4.073626</v>
       </c>
-      <c r="P135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P135" s="3" t="n">
+        <v>2.946948</v>
+      </c>
+      <c r="Q135" s="3" t="n">
+        <v>-0.749091</v>
       </c>
     </row>
   </sheetData>
@@ -8990,7 +8974,11 @@
           <t>Lease liabilities (note 11)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -11208,7 +11196,11 @@
           <t>Lease liabilities (note 14)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -33848,7 +33840,11 @@
           <t>Net cash (used in)/generated from operating activities</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -35588,7 +35584,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -37570,7 +37570,11 @@
           <t>Net cash generated from/(used in) operating activities</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -38976,7 +38980,11 @@
           <t>Net cash (used in) / generated from operating activities</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -46314,7 +46322,11 @@
           <t>Net cash generated from / (used in) operating activities</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -49934,7 +49946,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E444" s="5" t="n">
         <v>-0.6367080000000001</v>
       </c>
@@ -68976,7 +68992,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E644" s="5" t="n">
         <v>-0.6367080000000001</v>
       </c>
@@ -70308,7 +70328,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D658" t="inlineStr"/>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E658" s="5" t="n">
         <v>-0.6367080000000001</v>
       </c>
